--- a/data/trans_bre/IP43-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP43-Estudios-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 17,0</t>
+          <t>-3,41; 15,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 17,82</t>
+          <t>-2,24; 17,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 141,6</t>
+          <t>-17,18; 118,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 286,16</t>
+          <t>-21,05; 285,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 2,82</t>
+          <t>-5,81; 3,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 3,84</t>
+          <t>-3,03; 3,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,42; 12,71</t>
+          <t>-21,15; 14,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 36,58</t>
+          <t>-21,11; 35,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 6,93</t>
+          <t>-7,86; 6,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,32</t>
+          <t>-5,77; 4,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-32,86; 38,57</t>
+          <t>-32,14; 39,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,39; 62,95</t>
+          <t>-48,28; 53,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 3,03</t>
+          <t>-4,45; 2,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,6</t>
+          <t>-1,72; 3,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 14,12</t>
+          <t>-17,73; 13,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 35,85</t>
+          <t>-13,83; 35,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
